--- a/Pandas/nba.xlsx
+++ b/Pandas/nba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajes\Downloads\py-notes\Pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28D08EB-4E7A-4FA4-8489-BC889B0022A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92992525-90EE-42C5-BB11-0DA65635CA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16545065-DCAF-4AAC-B684-6435AE580BB1}"/>
   </bookViews>

--- a/Pandas/nba.xlsx
+++ b/Pandas/nba.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rajes\Downloads\py-notes\Pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92992525-90EE-42C5-BB11-0DA65635CA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573821E6-B20F-4EBF-840B-7AB43370DE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{16545065-DCAF-4AAC-B684-6435AE580BB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{16545065-DCAF-4AAC-B684-6435AE580BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="nba" sheetId="1" r:id="rId1"/>
+    <sheet name="nba (2)" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">nba!$A$1:$I$458</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'nba (2)'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="637">
   <si>
     <t>Name</t>
   </si>
@@ -15802,4 +15804,498 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC42720-091B-4FCB-BBFB-4EBFFD19FE19}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="G2">
+        <v>180</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>7730337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>99</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="G3">
+        <v>235</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <v>6796117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="G4">
+        <v>205</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="G5">
+        <v>185</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>1148640</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="G6">
+        <v>231</v>
+      </c>
+      <c r="I6">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="G7">
+        <v>240</v>
+      </c>
+      <c r="I7">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="G8">
+        <v>235</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>1170960</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9">
+        <v>238</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9">
+        <v>2165160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="G10">
+        <v>190</v>
+      </c>
+      <c r="H10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>1824360</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="G11">
+        <v>220</v>
+      </c>
+      <c r="H11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11">
+        <v>3431040</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>24</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="G12">
+        <v>260</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <v>2569260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13">
+        <v>27</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="G13">
+        <v>185</v>
+      </c>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13">
+        <v>6912869</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14">
+        <v>27</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G14">
+        <v>220</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14">
+        <v>3425510</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="G15">
+        <v>215</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15">
+        <v>1749840</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16">
+        <v>26</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16">
+        <v>253</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16">
+        <v>2616975</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>44</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17">
+        <v>27</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="G17">
+        <v>216</v>
+      </c>
+      <c r="I17">
+        <v>3425510</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>